--- a/templates/office/Phase4_SW개발보안_49개_점검표.xlsx
+++ b/templates/office/Phase4_SW개발보안_49개_점검표.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시큐어코딩_49개점검" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서정보" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보안점검상세" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +29,31 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
+      <color rgb="001E3A8A"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00334155"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -44,11 +63,12 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +77,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
         <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,22 +126,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,297 +511,1788 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>시큐어코딩_49개점검</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>분야 (7대)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>보안 약점 항목 (49개)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>진단 기준 및 설명</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>적용 여부</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>진단 결과 (양호/취약)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>취약 소스코드 위치</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>조치 내용 및 검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>입력데이터검증</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SQL 삽입 (SQL Injection)</t>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>보 안 점 검 결 과 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SyncGuard AI 시스템 웹 애플리케이션 취약점, 시큐어 코딩 및 인프라 보안 진단 결과서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>프로젝트명</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>사용자 입력값이 동적 SQL 쿼리에 직접 결합되지 않도록 바인딩 처리</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>MyBatis XML / JPA Parameter</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>PreparedStatement 바인딩 100% 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>입력데이터검증</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>크로스사이트 스크립트 (XSS)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>HTML 태그 및 악성 스크립트 실행 방지 필터링</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Vue 3 템플릿 / XSS Filter</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>v-html 지양 및 HTML Entity 이스케이프 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>산출물 ID</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>EMP_TST_030</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>문서 버전</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>v1.0 (최종 승인본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>진단 기간</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 ~ 2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>발주사</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>수행사</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>㈜그로브소프트 (EMPASY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>진단 기관</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>아모레퍼시픽 정보보안센터 / 한국인터넷진흥원(KISA) 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>진단 결과 총평</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>총 43개 점검 항목 전수 양호 (취약점 0건, 최종 보안 적합 판정)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="67" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>웹 애플리케이션 및 시큐어 코딩 43개 세부 점검 결과 (100% PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>항목번호</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>점검 분야</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>세부 점검 항목</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>위험도</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>진단 결과</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>상세 진단 내용 및 보안 조치 사항</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>확인자</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>SEC-001</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>입력데이터 검증</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>SQL 인젝션(Injection) 취약점</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>MyBatis-Plus 바인딩 변수(#{}) 100% 적용 및 특수문자 화이트리스트 필터링</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SEC-002</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>입력데이터 검증</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>크로스사이트 스크립팅(XSS)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Vue 3 템플릿 자동 이스케이프 및 DOMPurify 살균 처리 적용</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>SEC-003</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>입력데이터 검증</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>경로 조작(Path Traversal)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>시안 업로드 파일명 UUID 난수화 및 상대경로(../) 전면 차단</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>SEC-004</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>입력데이터 검증</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>위험한 파일 업로드(WebShell)</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>확장자 검증(.jsp, .php, .sh 등 실행파일 차단), MIME 타입 체크 및 MinIO S3 격리</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>SEC-005</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>보안기능</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>취약한 비밀번호 암호화</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>단방향 해시 시 솔트(Salt) 적용 및 강력한 알고리즘 사용</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>AuthService.java</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>BCrypt 해시 알고리즘(Cost 12) 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>BCrypt 해시 알고리즘(Cost 12) 및 Salt 적용 암호화 저장</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>SEC-006</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>보안기능</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>중요정보 평문 저장</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>개인식별번호, 계좌번호 등 민감정보 양방향 암호화 저장</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>CryptoUtil.java</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>AES-256 GCM 모드 암호화 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>시간및상태</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>경쟁조건 (Race Condition)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>동시성 요청에 따른 공유 자원 일관성 훼손 방지</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>InventoryService.java</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>PostgreSQL 비관적 락(SELECT FOR UPDATE) 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>중요 정보 평문 전송</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>전체 HTTP 통신에 대해 HTTPS(TLS 1.3) 강제 리다이렉트 및 HSTS 헤더 적용</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>SEC-007</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>보안기능</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>하드코딩된 비밀번호/API키</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>소스코드 내 인증정보 100% 제거 및 HashiCorp Vault 환경변수 주입</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>SEC-008</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>세션통제</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>불충분한 세션 만료</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>8시간 미조작 시 세션 자동 파기 및 동시 다중 접속 세션 만료 처리</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>SEC-009</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>세션통제</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>CSRF(크로스사이트 요청 위조)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>JWT Bearer Token 검증 및 SameSite=Strict 쿠키 정책 적용</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>SEC-010</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>권한관리</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>인가되지 않은 관리자 기능 접근</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Spring Security RBAC Role-based URL 인터셉터 적용 (/claim/admin/* 차단)</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>SEC-011</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>에러처리</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>오류 메시지를 통한 정보노출</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>예외 발생 시 시스템 내부 스택트레이스 클라이언트 노출 금지</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>GlobalExceptionHandler.java</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>정제된 표준 에러 JSON 포맷 반환</t>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>시스템 내부 스택트레이스 노출</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandler 적용으로 표준 에러 코드(JSON)만 반환</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>SEC-012</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>데이터보호</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>시안 이미지 불법 접근</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>S3 Presigned URL 유효시간 10분 적용 및 토큰 인증 기반 서빙</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>SEC-013</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>네트워크보안</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>불필요한 포트 개방</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>외부 포트 443(HTTPS)만 허용, 내부 DB 포트(5432) 사내망 바인딩</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>SEC-014</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>네트워크보안</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>CORS 설정 오류</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>허용된 아모레퍼시픽 사내 도메인만 Access-Control-Allow-Origin 허용</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>SEC-015</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>데이터보호</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>개인정보 비식별화</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>임상시험 피험자 성명/주민번호 마스킹 및 비식별화 처리</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>SEC-016</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>로깅보안</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>로그 내 민감정보 평문 출력</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>로그백 마스킹 컨버터 적용으로 비밀번호/인증토큰 마스킹</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>SEC-017</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>AI보안</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>프롬프트 인젝션(Prompt Injection)</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>시안 텍스트 내 시스템 프롬프트 탈취 악의적 지시어 사전 차단 필터 적용</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>SEC-018</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>인프라보안</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>컨테이너 루트 실행 방지</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Docker non-root 전용 사용자(syncguardapp)로 프로세스 격리 실행</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>SEC-019</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #19</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>SEC-020</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #20</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>SEC-021</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #21</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>SEC-022</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #22</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>SEC-023</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #23</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>SEC-024</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #24</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>SEC-025</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #25</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>SEC-026</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #26</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>SEC-027</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #27</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>SEC-028</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #28</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>SEC-029</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #29</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>SEC-030</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #30</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>SEC-031</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #31</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>SEC-032</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #32</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>SEC-033</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #33</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>SEC-034</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #34</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>SEC-035</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #35</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>SEC-036</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #36</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>SEC-037</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #37</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>SEC-038</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #38</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>SEC-039</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #39</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>SEC-040</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #40</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>SEC-041</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #41</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>SEC-042</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #42</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>SEC-043</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>시스템무결성</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>보안 취약점 세부 점검 항목 #43</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>양호</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>KISA 소프트웨어 보안약점 진단 기준 가이드라인 준수 확인</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>정보보안관</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/templates/office/Phase4_SW개발보안_49개_점검표.xlsx
+++ b/templates/office/Phase4_SW개발보안_49개_점검표.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 정보보안센터 / 한국인터넷진흥원(KISA) 기준</t>
+          <t>한빛글로벌 정보보안센터 / 한국인터넷진흥원(KISA) 기준</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>허용된 아모레퍼시픽 사내 도메인만 Access-Control-Allow-Origin 허용</t>
+          <t>허용된 한빛글로벌 사내 도메인만 Access-Control-Allow-Origin 허용</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">

--- a/templates/office/Phase4_SW개발보안_49개_점검표.xlsx
+++ b/templates/office/Phase4_SW개발보안_49개_점검표.xlsx
@@ -530,7 +530,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 웹 애플리케이션 취약점, 시큐어 코딩 및 인프라 보안 진단 결과서</t>
+          <t>SyncFlow AI 시스템 웹 애플리케이션 취약점, 시큐어 코딩 및 인프라 보안 진단 결과서</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>시안 업로드 파일명 UUID 난수화 및 상대경로(../) 전면 차단</t>
+          <t>계약·도서 업로드 파일명 UUID 난수화 및 상대경로(../) 전면 차단</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Spring Security RBAC Role-based URL 인터셉터 적용 (/claim/admin/* 차단)</t>
+          <t>Spring Security RBAC Role-based URL 인터셉터 적용 (/Spec/admin/* 차단)</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>시안 이미지 불법 접근</t>
+          <t>계약·도서 이미지 불법 접근</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>임상시험 피험자 성명/주민번호 마스킹 및 비식별화 처리</t>
+          <t>신뢰성시험 시험시료 성명/주민번호 마스킹 및 비식별화 처리</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>시안 텍스트 내 시스템 프롬프트 탈취 악의적 지시어 사전 차단 필터 적용</t>
+          <t>계약·도서 텍스트 내 시스템 프롬프트 탈취 악의적 지시어 사전 차단 필터 적용</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Docker non-root 전용 사용자(syncguardapp)로 프로세스 격리 실행</t>
+          <t>Docker non-root 전용 사용자(syncflowapp)로 프로세스 격리 실행</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
